--- a/data/satisfaction_detail/2026/1-8月/宴会.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/宴会.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.701967619216136</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.99</v>
+        <v>9.99305140228258</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.9</v>
+        <v>9.897428116429268</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.99</v>
+        <v>9.990735203043441</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98610280456516</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98610280456516</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.66</v>
+        <v>9.652678050075203</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97452180836946</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.708521631425285</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949043616738919</v>
       </c>
     </row>
     <row r="9">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.81</v>
+        <v>9.823671591612849</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.98</v>
+        <v>9.98610280456516</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949043616738919</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>10</v>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.504463416792003</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9.99</v>
+        <v>9.99305140228258</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.42</v>
+        <v>9.407090153056712</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97452180836946</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.92</v>
+        <v>9.924227196319562</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>10</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.138609218791473</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>10</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.59</v>
+        <v>9.5481995930284</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
